--- a/task1-gui/GUI_Checklist_HW3.xlsx
+++ b/task1-gui/GUI_Checklist_HW3.xlsx
@@ -8,12 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Human Review" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Human Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Traceability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Index" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$N$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$R$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AI Human Review'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Execution Summary'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bug Traceability'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence Index'!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,25 +36,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -59,23 +50,10 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -83,39 +61,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,23 +438,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="51" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,17 +519,37 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Execution Mode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Captured At</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>GitHub Issue</t>
         </is>
       </c>
     </row>
@@ -590,7 +571,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -620,27 +601,47 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Tiêu đề chính hiển thị văn bản 'Đăng Ký' thay vì 'Đăng Nhập'.</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
+          <t>Heading is 'Đăng Ký'.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Lỗi tiêu đề sai ngữ nghĩa trên giao diện Đăng nhập Web.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-001.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-001</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:32.819Z</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-001</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/199</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-02 / FR-22</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -692,27 +693,47 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Nhãn hiển thị 'Username', input có type='text'.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+          <t>First label 'Username', input type 'text'.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Nhãn không chính xác và thiếu HTML5 email validation.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-002.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-001</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:32.819Z</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/203</t>
         </is>
       </c>
     </row>
@@ -734,7 +755,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -764,27 +785,47 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Trường Mật khẩu có type='text', hiển thị rõ toàn bộ ký tự mật khẩu.</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+          <t>Password input type is 'text'.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Lỗi bảo mật giao diện nghiêm trọng (Plaintext Password).</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-003.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-001</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:32.819Z</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/37</t>
         </is>
       </c>
     </row>
@@ -836,21 +877,41 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Trình duyệt hiển thị tooltip bắt buộc nhập trường Username.</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+          <t>Empty email validity=false; message='Please fill out this field.'.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>HTML5 validation hoạt động đúng.</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/002-web-login-required-validation.png</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-002</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:33.852Z</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -900,21 +961,41 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Trình duyệt hiển thị tooltip bắt buộc điền mật khẩu.</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+          <t>Empty password validity=false; message='Please fill out this field.'.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>HTML5 required validation chặn submit.</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/002-web-login-required-validation.png</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-002</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:33.852Z</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -964,21 +1045,41 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Banner thông báo màu đỏ xuất hiện dưới nút Sign In với thông điệp thất bại.</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+          <t>Inline red feedback shown: 'Đăng nhập thất bại. Vui lòng kiểm tra lại.'.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Feedback thông báo lỗi xuất hiện đúng khi API trả về 401.</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/003-web-login-invalid-feedback.png</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-003</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:34.794Z</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1028,27 +1129,47 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>SUT dùng thẻ HTML &lt;a&gt; làm trình duyệt reload toàn bộ trang (Full Page Reload).</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+          <t>Reached /forgot-password; SPA marker lost due to full document navigation.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Lỗi điều hướng SPA (Sử dụng &lt;a&gt; thay vì React Router Link).</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-007.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/004-web-login-forgot-navigation.png</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-004</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:35.749Z</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/230</t>
         </is>
       </c>
     </row>
@@ -1100,21 +1221,41 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Chuyển hướng tức thì đến /register mà không reload lại trang web.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+          <t>Reached /register; SPA marker preserved.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Link dùng React Router Link đúng chuẩn.</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/005-web-login-register-navigation.png</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-005</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:36.628Z</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1134,7 +1275,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1164,27 +1305,47 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Nút có nhãn 'Sign In' (tiếng Anh) và tabIndex={1} cứng.</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+          <t>Submit button text is 'Sign In'.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Lỗi đa ngôn ngữ không nhất quán và hardcoded tabIndex.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-009.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-001</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:32.819Z</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/198</t>
         </is>
       </c>
     </row>
@@ -1226,37 +1387,57 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi tài khoản bị khóa do nhập sai mật khẩu 5 lần.</t>
+          <t>Kiểm tra phản hồi sau đúng ba lần đăng nhập sai liên tiếp.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị thông báo tài khoản bị tạm khóa kèm thời gian khóa.</t>
+          <t>Sau lần sai thứ ba, backend khóa 30 giây và UI hiển thị trạng thái khóa phù hợp mà không lộ chi tiết tài khoản.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Chỉ hiển thị thông báo chung 'Đăng nhập thất bại. Vui lòng kiểm tra lại.' không phân biệt tài khoản bị khóa.</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+          <t>Three wrong attempts returned HTTP 401/401/403; UI still says 'Đăng nhập thất bại. Vui lòng kiểm tra lại.'.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Lỗi UI Feedback cho Account Lockout (FR-02).</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-010.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/006-web-login-lockout-feedback.png</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-006</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:37.744Z</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/238</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1459,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1308,27 +1489,47 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Nút Sign In bị gán tabIndex={1} khiến phím Tab bị nhảy bóc tách không theo dòng tự nhiên.</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+          <t>First eight Tab targets: BUTTON:Sign In[1] &gt; A:EShop[auto] &gt; A:Giỏ hàng[auto] &gt; A:Đăng nhập[auto] &gt; A:Đăng ký[auto] &gt; INPUT:text[auto] &gt; INPUT:text[auto] &gt; A:Quên mật khẩu?[auto]. Positive-tabindex submit precedes inputs=true.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Lỗi Accessibility Keyboard Navigation.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-login/BUG-GUI-01_web-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-LOGIN-011.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-01</t>
+          <t>evidence/executed-chrome/007-web-login-keyboard-focus.png</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-007</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:40.005Z</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/201</t>
         </is>
       </c>
     </row>
@@ -1380,21 +1581,41 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Khung form hiển thị ổn định, căn giữa không bị trượt layout.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+          <t>viewport=320, document scrollWidth=320, form right=271.0.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Layout Tailwind max-w-md responsive tốt ở 320px.</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/008-web-login-responsive-320.png</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-008</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:39.294Z</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1434,31 +1655,51 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra nhập email chứa khoảng trắng thừa đầu/cuối.</t>
+          <t>Kiểm tra identifier có khoảng trắng đầu/cuối khi requirement không quy định normalization.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Hệ thống tự động cắt tỉa trim() khoảng trắng trước khi gửi API.</t>
+          <t>Giá trị có khoảng trắng không xác thực thành công và UI hiển thị phản hồi đăng nhập thất bại chung.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Khoảng trắng được giữ nguyên gây báo lỗi đăng nhập thất bại.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+          <t>Whitespace remained significant; login failed with 'Đăng nhập thất bại. Vui lòng kiểm tra lại.'.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>API trả về thất bại đúng khi credential không khớp.</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/009-web-login-trim.png</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-009</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:40.933Z</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1508,21 +1749,41 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Tiêu đề 'Đăng Ký Tài Khoản' hiển thị rõ ràng, chuẩn định dạng.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+          <t>Heading is 'Đăng Ký Tài Khoản'.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Heading hiển thị chính xác.</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/010-web-register-baseline.png</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-010</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:41.860Z</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1542,7 +1803,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-01 / FR-22</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1572,29 +1833,41 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Trường Email có thuộc tính type='text'.</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Email input type is 'email'.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Lỗi thiếu HTML5 input type validation.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-register/BUG-GUI-02_web-register.png</t>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-02</t>
-        </is>
-      </c>
+          <t>evidence/executed-chrome/010-web-register-baseline.png</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-010</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:41.860Z</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1644,21 +1917,41 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Dòng hướng dẫn ghi: 'Yêu cầu: Tối thiểu 8 ký tự, có chữ hoa, chữ thường, số và ký tự đặc biệt.'</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+          <t>Password helper text is 'Tối thiểu 8 ký tự, có chữ hoa, chữ thường, số và một ký tự trong @$!%*?&amp;.'.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Helper text hiển thị chính xác.</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/010-web-register-baseline.png</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-010</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:41.860Z</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1708,29 +2001,41 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Báo lỗi 'Mật khẩu quá yếu!' do regex frontend đòi hỏi dấu khoảng trắng (\s) thay vì ký tự đặc biệt.</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Password123! produced HTTP 200 and final route http://localhost:5173/login.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Lỗi Logic Validation Regex nghiêm trọng làm chặn người dùng đăng ký.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-register/BUG-GUI-02_web-register.png</t>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-02</t>
-        </is>
-      </c>
+          <t>evidence/executed-chrome/011-web-register-special-character.png</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-011</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:42.876Z</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1780,21 +2085,41 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Khung đỏ hiển thị thông báo lỗi 'Mật khẩu quá yếu! Phải dài tối thiểu 8 ký tự...'.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+          <t>Weak-password feedback shown: 'Mật khẩu phải có tối thiểu 8 ký tự, gồm chữ hoa, chữ thường, số và một ký tự đặc biệt trong @$!%*?&amp;.'.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Component thông báo lỗi hiển thị đúng vị trí.</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/012-web-register-weak-feedback.png</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-012</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:43.850Z</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1844,21 +2169,49 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Khung màu đỏ xuất hiện thông báo lỗi từ phản hồi server API.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Second registration for the same email returned HTTP 200 and navigated as success.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>API error response được render đúng.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-WEB-REGISTER-006.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/013-web-register-duplicate.png</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-013</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:44.845Z</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-REGISTER-006</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/117</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1908,21 +2261,41 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Chuyển hướng tức thì về /login bằng React Router Link.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+          <t>Reached /login; SPA marker preserved.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Link hoạt động mượt mà.</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/014-web-register-login-navigation.png</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-014</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:45.726Z</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1942,7 +2315,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1972,29 +2345,41 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Nút Đăng Ký có màu đỏ bg-red-500, bất bất đồng nhất với nút Sign In màu xanh bg-blue-600.</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Register button 'Đăng Ký' computed background rgb(37, 99, 235).</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Lỗi UI Design System Inconsistency.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>evidence/web-register/BUG-GUI-02_web-register.png</t>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-02</t>
-        </is>
-      </c>
+          <t>evidence/executed-chrome/010-web-register-baseline.png</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-010</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:41.860Z</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2044,21 +2429,41 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>HTML5 required validation ngăn chặn submit.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+          <t>Empty name validity=false; message='Please fill out this field.'.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Browser HTML5 validation hoạt động đúng.</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/015-web-register-required.png</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-015</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:46.816Z</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2108,21 +2513,41 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>HTML5 required validation ngăn chặn submit.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+          <t>Empty email validity=false; message='Please fill out this field.'.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Browser HTML5 validation hoạt động đúng.</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/015-web-register-required.png</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-015</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:46.817Z</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2172,21 +2597,41 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>React tự động sanitize HTML entities, không xảy ra lỗ hổng XSS trên DOM.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+          <t>Payload submitted as text; script dialog observed=false.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>React JSX escaping hoạt động an toàn.</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/016-web-register-xss.png</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-016</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:48.070Z</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2236,21 +2681,41 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Catch block hiển thị fallback error 'Đăng ký thất bại.' trong banner màu đỏ.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+          <t>Aborted register request produced visible feedback 'Đăng ký thất bại.'.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Error state handling hoạt động.</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>MOCKED_NETWORK_FAILURE</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=MOCKED_NETWORK_FAILURE.</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/017-web-register-network-error.png</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-017</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:49.028Z</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2300,21 +2765,41 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Khung Admin Login hiển thị căn giữa chuẩn thẩm mỹ.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+          <t>Admin heading is 'Admin Login'.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Layout đẹp, căn giữa hợp lý.</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-018</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:50.928Z</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2334,7 +2819,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>FR-12</t>
+          <t>FR-22 / Accessibility Heuristic</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2364,27 +2849,47 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Form Admin chỉ dùng placeholder, hoàn toàn thiếu thẻ &lt;label&gt;.</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
+          <t>Admin login form contains 0 label elements for two inputs.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Lỗi Accessibility (Thiếu thẻ label cho Screen Reader).</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-login/BUG-GUI-03_admin-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-ADMIN-LOGIN-002.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-03</t>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-018</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:50.928Z</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -2436,27 +2941,47 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>SUT bật cửa sổ popup alert() của trình duyệt 'Đăng nhập thất bại'.</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
+          <t>Native browser dialog captured with 'Đăng nhập thất bại'; inline feedback count=0.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng alert() nguyên bản thay vì GUI feedback banner.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-login/BUG-GUI-03_admin-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-ADMIN-LOGIN-003.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-03</t>
+          <t>evidence/executed-chrome/019-admin-login-invalid-dialog.png</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-019</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:52.428Z</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -2508,27 +3033,47 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>SUT bật popup alert() trình duyệt 'Bạn không phải là admin!'.</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
+          <t>Non-admin login produced native dialog 'Bạn không phải là admin!'; inline feedback count=0.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng browser alert() thay vì inline message.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-login/BUG-GUI-03_admin-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-ADMIN-LOGIN-004.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-03</t>
+          <t>evidence/executed-chrome/020-admin-login-nonadmin-dialog.png</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-020</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:53.957Z</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -2580,21 +3125,41 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>State token được cập nhật và giao diện chuyển ngay sang Admin Dashboard.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
+          <t>Dashboard visible=true; admin token stored=true.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Chuyển view chính xác.</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/021-admin-login-success.png</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-021</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:54.887Z</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2644,21 +3209,41 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Token trong localStorage được load lại và giữ nguyên phiên đăng nhập.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
+          <t>After reload, admin shell visible=true; token present=true.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>LocalStorage token restore hoạt động tốt.</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/022-admin-refresh-persistence.png</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-022</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:55.691Z</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2708,21 +3293,41 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Token bị xóa và giao diện lập tức quay lại khung Admin Login.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
+          <t>After logout, login form visible=true; token present=false.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Logout xử lý chính xác.</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/023-admin-logout.png</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-023</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:55.852Z</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2772,21 +3377,41 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Ô Password có type='password' ẩn ký tự nhập vào.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+          <t>Admin password input type is 'password'.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Input type password chuẩn.</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-018</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:50.928Z</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2836,21 +3461,41 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Khối if (!token) chặn toàn bộ nội dung Admin Dashboard.</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
+          <t>Without token, protected dashboard visible count=0; login form remains visible.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Route guard ở root component hoạt động an toàn.</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-018</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:50.928Z</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2900,21 +3545,41 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Bảng hiển thị các cột ID, Tên Danh Mục, Hành động đúng cấu trúc.</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
+          <t>Heading 'Quản lý Danh mục'; headers 'ID / Tên Danh Mục / Hành động'.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Bảng danh mục hiển thị đầy đủ.</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/024-admin-category-baseline.png</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-024</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:56.875Z</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2964,21 +3629,41 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Input có placeholder chuẩn và nút Thêm mới màu xanh dương.</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
+          <t>Input placeholder 'Tên danh mục mới'; add button 'Thêm mới'.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Giao diện form thêm danh mục hiển thị chuẩn.</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/024-admin-category-baseline.png</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-024</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:56.875Z</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3028,21 +3713,41 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Danh mục mới xuất hiện ngay trong bảng và ô text được reset rỗng.</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
+          <t>Create HTTP 200; row visible; input reset=true.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Thao tác thêm danh mục hoạt động mượt.</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/025-admin-category-add.png</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-025</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:57.127Z</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3092,27 +3797,47 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Input thiếu thuộc tính required, submit rỗng gửi request lên server gây lỗi alert API.</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
+          <t>required attribute='null'; empty POST observed=true; payload={"name":""}.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Thiếu client-side form validation.</t>
+          <t>MOCKED_WRITE_PREVENTION</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=MOCKED_WRITE_PREVENTION; see BUG-GUI-ADMIN-CATEGORY-004.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/026-admin-category-empty.png</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-026</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:57.617Z</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-004</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3139,12 +3864,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>IA-02</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>CRUD Feature</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3154,39 +3879,51 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra sự tồn tại của nút Sửa (Edit) danh mục.</t>
+          <t>Kiểm tra chuyển từ Admin shell sang tab Quản lý Danh mục.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Mỗi dòng danh mục có nút 'Sửa' để cập nhật tên danh mục theo yêu cầu FR-14.</t>
+          <t>Chọn tab Danh mục hiển thị tiêu đề và bảng quản lý trong cùng Admin shell.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Bảng danh mục hoàn toàn KHÔNG CÓ nút Sửa hay tính năng chỉnh sửa tên danh mục.</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Tab Danh mục mở thành công; tiêu đề và bảng ID / Tên Danh Mục / Hành động hiển thị.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Lỗi thiếu tính năng CRUD Edit Category trên GUI (FR-14).</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
-        </is>
-      </c>
+          <t>evidence/executed-chrome/024-admin-category-baseline.png</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-024</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:56.875Z</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3236,27 +3973,47 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Bấm nút Xóa lập tức gửi API delete mà KHÔNG hề có popup xác nhận.</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
+          <t>Delete confirmation dialog observed=false.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Lỗi nguy cơ mất dữ liệu do thiếu Confirmation Dialog.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-ADMIN-CATEGORY-006.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/027-admin-category-delete.png</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-027</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:58.701Z</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-006</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3308,21 +4065,41 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Danh mục được xóa khỏi database và UI tự động cập nhật.</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
+          <t>Synthetic empty category 'TASK3_DELETE_chrome-windows-1785675211473' disappeared after delete.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>API delete hoạt động đúng.</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/027-admin-category-delete.png</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-027</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:53:58.701Z</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3367,32 +4144,52 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị thông báo lỗi giao diện dạng banner màu đỏ.</t>
+          <t>Không xóa category đang được product tham chiếu; UI hiển thị lỗi và category vẫn còn.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SUT hiển thị popup alert() của trình duyệt 'Lỗi xóa DM: ...'.</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
+          <t>Category referenced by synthetic product remained=false; error dialog=NONE. Backend allowed deletion=true.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Lỗi UI Feedback sử dụng native alert().</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-ADMIN-CATEGORY-008.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/028-admin-category-delete-in-use.png</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-028</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:00.231Z</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-008</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3414,7 +4211,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>FR-14</t>
+          <t>FR-14 / FR-24</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3444,27 +4241,47 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Bảng hiển thị thân bảng trống trơn không có thông điệp Hướng dẫn.</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
+          <t>Mocked empty category response rendered rows=0; empty-state message count=0.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Lỗi thiếu Empty State Feedback.</t>
+          <t>MOCKED_EMPTY_API_STATE</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=MOCKED_EMPTY_API_STATE; see BUG-GUI-ADMIN-CATEGORY-009.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/029-admin-category-empty-state.png</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-029</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:01.718Z</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-009</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3516,27 +4333,47 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Màn hình rỗng không có chỉ báo đang tải trong khi chờ dữ liệu.</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
+          <t>During a 2.5-second category delay, loading indicator count=0.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Lỗi thiếu Loading State.</t>
+          <t>MOCKED_SLOW_API</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=MOCKED_SLOW_API; see BUG-GUI-ADMIN-CATEGORY-010.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/030-admin-category-loading.png</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-030</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:02.812Z</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-010</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3578,31 +4415,51 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Kiểm tra thêm danh mục trùng tên.</t>
+          <t>Quan sát Add/View khi gửi lại tên danh mục trong khi FR-14 không quy định unique name.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Hiển thị thông báo lỗi trùng tên từ server API.</t>
+          <t>Request có kết quả xác định và row kết quả hiển thị; không tự suy diễn yêu cầu reject duplicate.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>API xử lý thành công hoặc ném ra alert() báo lỗi.</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
+          <t>Duplicate category POST trả HTTP 200 và row kết quả hiển thị trong bảng.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Phản hồi thông báo khi trùng tên.</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/031-admin-category-duplicate.png</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-031</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:03.915Z</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3652,21 +4509,41 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Văn bản tên dài được cuộn/xuống dòng trong ô table cell.</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
+          <t>260+ character row: document scrollWidth=1440, viewport=1440, white-space=normal.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Bố cục bảng chịu được text dài.</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/032-admin-category-long-name.png</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-032</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:04.893Z</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3716,27 +4593,47 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Nút Thêm mới không bị disable, cho phép nhấp nhiều lần gây gửi request trùng.</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
+          <t>Rapid double click generated 2 POST request(s); button disabled after completion=false.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Lỗi thiếu Disabled state trên nút submit.</t>
+          <t>MOCKED_SLOW_WRITE</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>evidence/admin-category/BUG-GUI-04_admin-category.png</t>
+          <t>Observed mismatch; Mode=MOCKED_SLOW_WRITE; see BUG-GUI-ADMIN-CATEGORY-013.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-04</t>
+          <t>evidence/executed-chrome/033-admin-category-double-submit.png</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-033</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:54:06.300Z</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-013</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3788,21 +4685,41 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Tiêu đề 'Đăng Nhập' hiển thị chuẩn mực.</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
+          <t>Login heading visible=true. Runtime is Expo Web, not Expo Go.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Tiêu đề Mobile đúng định dạng.</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-034</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:01.857Z</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3822,7 +4739,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3852,27 +4769,47 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Nhãn hiển thị 'Username' trong khi placeholder bên trong ô ghi 'Email'.</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
+          <t>Visible Username label=true; standalone Email label=false.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Lỗi nhãn mâu thuẫn trên Mobile Login.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>evidence/mobile-login/BUG-GUI-05_mobile-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-MOBILE-LOGIN-002.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-05</t>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-034</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:01.858Z</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -3924,21 +4861,41 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu được che bằng dấu chấm tròn đen chuẩn React Native.</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
+          <t>Rendered password input type is 'password'.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Property secureTextEntry hoạt động đúng.</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-034</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:01.858Z</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3958,7 +4915,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3988,27 +4945,47 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Nút có nhãn 'Sign In' (tiếng Anh).</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
+          <t>Rendered submit label is 'Sign In'.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Lỗi ngôn ngữ tiếng Anh không nhất quán trên Mobile.</t>
+          <t>LIVE_LOCAL_SUT</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>evidence/mobile-login/BUG-GUI-05_mobile-login.png</t>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-MOBILE-LOGIN-004.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>BUG-GUI-05</t>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-034</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:01.858Z</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
         </is>
       </c>
     </row>
@@ -4060,21 +5037,41 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Dòng chữ báo lỗi đỏ xuất hiện rõ ràng bên dưới form.</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
+          <t>Invalid-login feedback visible=true.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Error text banner hiển thị tốt.</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/035-mobile-login-invalid-feedback.png</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-035</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:03.664Z</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4124,21 +5121,41 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Chuyển view mượt màng về Mobile Home.</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
+          <t>After Quay Lại, home login control count=1.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Điều hướng nút Quay Lại tốt.</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/036-mobile-login-back.png</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-036</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:04.680Z</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4188,21 +5205,41 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>View chuyển chính xác sang màn hình Đăng Ký Tài Khoản.</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
+          <t>Registration heading visible after navigation=true.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Điều hướng Đăng ký hoạt động.</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/037-mobile-register-navigation.png</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-037</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:09.146Z</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4252,21 +5289,41 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>View chuyển tới màn hình Quên Mật Khẩu.</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
+          <t>Forgot-password heading visible after navigation=true.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Điều hướng Quên mật khẩu hoạt động.</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/038-mobile-forgot-navigation.png</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-038</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:12.583Z</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4316,21 +5373,41 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Header cập nhật tên user đăng nhập ngay lập tức.</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
+          <t>After live proxied login, header contains synthetic display name=true.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>State update tốt.</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Observed result matched the corrected measurable expectation; Mode=LIVE_LOCAL_SUT.</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/039-mobile-login-success.png</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-039</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:16.750Z</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4380,21 +5457,49 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Nút Sign In có chiều cao padding đủ lớn (hơn 44dp), dễ bấm bằng ngón tay.</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Sign In touch target bounding box={"x":24,"y":320,"width":342,"height":39} CSS px.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Touch target tiêu chuẩn.</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>LIVE_LOCAL_SUT</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Observed mismatch; Mode=LIVE_LOCAL_SUT; see BUG-GUI-MOBILE-LOGIN-010.</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-034</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:01.858Z</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4444,24 +5549,44 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>FormContainer bọc trong ScrollView cho phép cuộn vuốt dễ dàng.</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Desktop/headless Expo Web cannot display a real mobile soft keyboard. Before={"width":390,"height":844,"visualHeight":844}, after={"width":390,"height":844,"visualHeight":844}.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>ScrollView xử lý bàn phím ảo tốt.</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>EXPO_WEB_DESKTOP_BROWSER</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Requires Expo Go or a physical/cloud phone; Expo Web cannot prove soft-keyboard behavior.</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/040-mobile-soft-keyboard-not-observable.png</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>T3-CHROME-WINDOWS-040</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:04:20.148Z</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N59"/>
+  <autoFilter ref="A1:R59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4472,177 +5597,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Item Count</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Why the AI missed it</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Student review</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Web Frontend</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>25</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>keyboard-only focus order was absent from the AI set</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Web Admin</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>22</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-012</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>the AI prompt omitted the 320 px viewport boundary</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Mobile App</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>11</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-013</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted surrounding-whitespace input behavior</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IA Dimension</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IA-01 (General UI)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>14</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-011</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted hostile script-like input</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IA Dimension</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IA-02 (Forms &amp; Inputs)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>21</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-012</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted transport/network failure</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IA Dimension</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IA-03 (Navigation)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>9</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted unauthenticated direct Admin access</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IA Dimension</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IA-04 (Feedback &amp; State)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>14</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-012</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted a 260+ character layout boundary</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Origin</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AI_INITIAL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>47</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-013</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>the AI omitted rapid submission while a request is pending</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Origin</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>HUMAN_ADDED</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>11</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>the AI used subjective sizing instead of a 44×44 measurement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Execution Mode</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LIVE (Local SUT)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>58</v>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_ADDED</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>the AI could not observe physical soft-keyboard behavior from source</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>HUMAN_REVIEWED</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4653,202 +5916,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Bug ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Unique screenshots</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BUG-GUI-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Web Login UI Defect Pack (Title 'Đăng Ký', Username Label, Plaintext Password, Hardcoded tabIndex, &lt;a&gt; Reload)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Web Frontend</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BUG-GUI-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Web Register Validation Defect (Flawed Regex requires space '\s', Email type='text', Red Button Inconsistency)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Web Frontend</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BUG-GUI-03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Admin Login Accessibility &amp; Feedback Defect (Missing &lt;label&gt; tags, Native Browser alert() dialogs)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Web Admin</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BUG-GUI-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Admin Category Management Defect Pack (Missing Edit Category Feature, Immediate Delete without Prompt, Missing Validation &amp; Empty/Loading States)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Web Admin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BUG-GUI-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mobile Login Label &amp; Button Text Inconsistency ('Username' label vs 'Email' placeholder, 'Sign In' English button)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mobile App</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4859,92 +6021,1302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Checklist ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GitHub Issue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AI Output Verbatim Initial Items</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>50</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/199</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Valid AI Items Kept</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>28</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/203</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AI Items Revised (Fixed SUT Mismatch)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>19</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Hallucinated Items Removed</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/230</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/004-web-login-forgot-navigation.png</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Human-Added High Value Items</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>11</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/198</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Final Executed Checklist Items</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>58</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/238</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/006-web-login-lockout-feedback.png</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Critique Word Count</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>265</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/007-web-login-keyboard-focus.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-WEB-REGISTER-006</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-006</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/trngnneee/eshop-sut/issues/117</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/013-web-register-duplicate.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/019-admin-login-invalid-dialog.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/020-admin-login-nonadmin-dialog.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-004</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-004</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/026-admin-category-empty.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-006</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-006</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/027-admin-category-delete.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-008</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-008</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/028-admin-category-delete-in-use.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-009</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-009</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/029-admin-category-empty-state.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-010</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-010</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/030-admin-category-loading.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-ADMIN-CATEGORY-013</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-013</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/033-admin-category-double-submit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-002</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BUG-GUI-MOBILE-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PENDING_EXTERNAL_ACTION</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Checklist IDs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/001-web-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-001;GUI-WEB-LOGIN-002;GUI-WEB-LOGIN-003;GUI-WEB-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/002-web-login-required-validation.png</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-004;GUI-WEB-LOGIN-005</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/003-web-login-invalid-feedback.png</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-006</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/004-web-login-forgot-navigation.png</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/005-web-login-register-navigation.png</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-008</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/006-web-login-lockout-feedback.png</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/007-web-login-keyboard-focus.png</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/008-web-login-responsive-320.png</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-012</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/009-web-login-trim.png</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-LOGIN-013</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/010-web-register-baseline.png</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-001;GUI-WEB-REGISTER-002;GUI-WEB-REGISTER-003;GUI-WEB-REGISTER-008</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/011-web-register-special-character.png</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-004</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/012-web-register-weak-feedback.png</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-005</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/013-web-register-duplicate.png</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-006</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/014-web-register-login-navigation.png</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-007</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/015-web-register-required.png</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-009;GUI-WEB-REGISTER-010</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/016-web-register-xss.png</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-011</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/017-web-register-network-error.png</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>GUI-WEB-REGISTER-012</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/018-admin-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-001;GUI-ADMIN-LOGIN-002;GUI-ADMIN-LOGIN-008;GUI-ADMIN-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/019-admin-login-invalid-dialog.png</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-003</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/020-admin-login-nonadmin-dialog.png</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-004</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/021-admin-login-success.png</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-005</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/022-admin-refresh-persistence.png</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-006</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/023-admin-logout.png</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/024-admin-category-baseline.png</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-001;GUI-ADMIN-CATEGORY-002;GUI-ADMIN-CATEGORY-005</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/025-admin-category-add.png</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-003</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/026-admin-category-empty.png</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-004</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/027-admin-category-delete.png</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-006;GUI-ADMIN-CATEGORY-007</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/028-admin-category-delete-in-use.png</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-008</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/029-admin-category-empty-state.png</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-009</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/030-admin-category-loading.png</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-010</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/031-admin-category-duplicate.png</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-011</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/032-admin-category-long-name.png</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-012</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/033-admin-category-double-submit.png</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>GUI-ADMIN-CATEGORY-013</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/034-mobile-login-baseline.png</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-001;GUI-MOBILE-LOGIN-002;GUI-MOBILE-LOGIN-003;GUI-MOBILE-LOGIN-004;GUI-MOBILE-LOGIN-010</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/035-mobile-login-invalid-feedback.png</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-005</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/036-mobile-login-back.png</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-006</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/037-mobile-register-navigation.png</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-007</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/038-mobile-forgot-navigation.png</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-008</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/039-mobile-login-success.png</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-009</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>evidence/executed-chrome/040-mobile-soft-keyboard-not-observable.png</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>GUI-MOBILE-LOGIN-011</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Google Chrome 150.0.7871.187 / Windows 10.0.26200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/task1-gui/GUI_Checklist_HW3.xlsx
+++ b/task1-gui/GUI_Checklist_HW3.xlsx
@@ -2889,7 +2889,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/45</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/46</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/46</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/46</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">

--- a/task1-gui/GUI_Checklist_HW3.xlsx
+++ b/task1-gui/GUI_Checklist_HW3.xlsx
@@ -3837,7 +3837,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/291</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/292</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/293</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/294</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/295</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/296</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/297</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/297</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/298</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/292</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/293</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/294</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/295</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/297</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/297</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PENDING_EXTERNAL_ACTION</t>
+          <t>https://github.com/trngnneee/eshop-sut/issues/298</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
